--- a/data/adattabla.xlsx
+++ b/data/adattabla.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MUNKA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasko\datHU\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA3DADD-011D-48C0-9D4D-EA3C7AF29A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEDF3A8-C851-4DFD-8AB2-30B680830135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F544247-7894-42D1-8E38-07F7BA1C1A12}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t>Időszak</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Partner</t>
-  </si>
-  <si>
-    <t>Augusztus</t>
   </si>
   <si>
     <t>szeptember</t>
@@ -91,9 +88,6 @@
   </si>
   <si>
     <t>augusztus</t>
-  </si>
-  <si>
-    <t>4Control Kft</t>
   </si>
   <si>
     <t>DEKRA-Expert Kft.</t>
@@ -166,6 +160,9 @@
   </si>
   <si>
     <t>2026. február</t>
+  </si>
+  <si>
+    <t>4Control Kft.</t>
   </si>
 </sst>
 </file>
@@ -413,20 +410,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -437,25 +422,25 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hivatkozás" xfId="2" builtinId="8"/>
-    <cellStyle name="Normál" xfId="0" builtinId="0"/>
-    <cellStyle name="Százalék" xfId="1" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -467,6 +452,18 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -486,7 +483,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="hu-HU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1820,7 +1817,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="hu-HU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1992,49 +1989,49 @@
               <c:strCache>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>2023/ július</c:v>
+                  <c:v>2023. július</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023/ augusztus</c:v>
+                  <c:v>2023. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023/ szeptember</c:v>
+                  <c:v>2023. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2023/ október</c:v>
+                  <c:v>2023. október</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2023/ november</c:v>
+                  <c:v>2023. november</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2023/ december</c:v>
+                  <c:v>2023. december</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2024/ január</c:v>
+                  <c:v>2024. január</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2024/ február</c:v>
+                  <c:v>2024. február</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2024/ március</c:v>
+                  <c:v>2024. március</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2024/ április</c:v>
+                  <c:v>2024. április</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2024/ május</c:v>
+                  <c:v>2024. május</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2024/ június</c:v>
+                  <c:v>2024. június</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2024/ július</c:v>
+                  <c:v>2024. július</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2024/ augusztus</c:v>
+                  <c:v>2024. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2024/ szeptember</c:v>
+                  <c:v>2024. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2024. október</c:v>
@@ -2223,49 +2220,49 @@
               <c:strCache>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>2023/ július</c:v>
+                  <c:v>2023. július</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023/ augusztus</c:v>
+                  <c:v>2023. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023/ szeptember</c:v>
+                  <c:v>2023. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2023/ október</c:v>
+                  <c:v>2023. október</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2023/ november</c:v>
+                  <c:v>2023. november</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2023/ december</c:v>
+                  <c:v>2023. december</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2024/ január</c:v>
+                  <c:v>2024. január</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2024/ február</c:v>
+                  <c:v>2024. február</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2024/ március</c:v>
+                  <c:v>2024. március</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2024/ április</c:v>
+                  <c:v>2024. április</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2024/ május</c:v>
+                  <c:v>2024. május</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2024/ június</c:v>
+                  <c:v>2024. június</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2024/ július</c:v>
+                  <c:v>2024. július</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2024/ augusztus</c:v>
+                  <c:v>2024. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2024/ szeptember</c:v>
+                  <c:v>2024. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2024. október</c:v>
@@ -2511,7 +2508,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="hu-HU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2664,49 +2661,49 @@
               <c:strCache>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>2023/ július</c:v>
+                  <c:v>2023. július</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023/ augusztus</c:v>
+                  <c:v>2023. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023/ szeptember</c:v>
+                  <c:v>2023. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2023/ október</c:v>
+                  <c:v>2023. október</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2023/ november</c:v>
+                  <c:v>2023. november</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2023/ december</c:v>
+                  <c:v>2023. december</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2024/ január</c:v>
+                  <c:v>2024. január</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2024/ február</c:v>
+                  <c:v>2024. február</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2024/ március</c:v>
+                  <c:v>2024. március</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2024/ április</c:v>
+                  <c:v>2024. április</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2024/ május</c:v>
+                  <c:v>2024. május</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2024/ június</c:v>
+                  <c:v>2024. június</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2024/ július</c:v>
+                  <c:v>2024. július</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2024/ augusztus</c:v>
+                  <c:v>2024. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2024/ szeptember</c:v>
+                  <c:v>2024. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2024. október</c:v>
@@ -2895,49 +2892,49 @@
               <c:strCache>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>2023/ július</c:v>
+                  <c:v>2023. július</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023/ augusztus</c:v>
+                  <c:v>2023. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023/ szeptember</c:v>
+                  <c:v>2023. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2023/ október</c:v>
+                  <c:v>2023. október</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2023/ november</c:v>
+                  <c:v>2023. november</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2023/ december</c:v>
+                  <c:v>2023. december</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2024/ január</c:v>
+                  <c:v>2024. január</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2024/ február</c:v>
+                  <c:v>2024. február</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2024/ március</c:v>
+                  <c:v>2024. március</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2024/ április</c:v>
+                  <c:v>2024. április</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2024/ május</c:v>
+                  <c:v>2024. május</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2024/ június</c:v>
+                  <c:v>2024. június</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2024/ július</c:v>
+                  <c:v>2024. július</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2024/ augusztus</c:v>
+                  <c:v>2024. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2024/ szeptember</c:v>
+                  <c:v>2024. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2024. október</c:v>
@@ -3183,7 +3180,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="hu-HU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3344,49 +3341,49 @@
               <c:strCache>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>2023/ július</c:v>
+                  <c:v>2023. július</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023/ augusztus</c:v>
+                  <c:v>2023. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023/ szeptember</c:v>
+                  <c:v>2023. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2023/ október</c:v>
+                  <c:v>2023. október</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2023/ november</c:v>
+                  <c:v>2023. november</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2023/ december</c:v>
+                  <c:v>2023. december</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2024/ január</c:v>
+                  <c:v>2024. január</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2024/ február</c:v>
+                  <c:v>2024. február</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2024/ március</c:v>
+                  <c:v>2024. március</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2024/ április</c:v>
+                  <c:v>2024. április</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2024/ május</c:v>
+                  <c:v>2024. május</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2024/ június</c:v>
+                  <c:v>2024. június</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2024/ július</c:v>
+                  <c:v>2024. július</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2024/ augusztus</c:v>
+                  <c:v>2024. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2024/ szeptember</c:v>
+                  <c:v>2024. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2024. október</c:v>
@@ -3575,49 +3572,49 @@
               <c:strCache>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>2023/ július</c:v>
+                  <c:v>2023. július</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023/ augusztus</c:v>
+                  <c:v>2023. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023/ szeptember</c:v>
+                  <c:v>2023. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2023/ október</c:v>
+                  <c:v>2023. október</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2023/ november</c:v>
+                  <c:v>2023. november</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2023/ december</c:v>
+                  <c:v>2023. december</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2024/ január</c:v>
+                  <c:v>2024. január</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2024/ február</c:v>
+                  <c:v>2024. február</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2024/ március</c:v>
+                  <c:v>2024. március</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2024/ április</c:v>
+                  <c:v>2024. április</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2024/ május</c:v>
+                  <c:v>2024. május</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2024/ június</c:v>
+                  <c:v>2024. június</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2024/ július</c:v>
+                  <c:v>2024. július</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2024/ augusztus</c:v>
+                  <c:v>2024. augusztus</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2024/ szeptember</c:v>
+                  <c:v>2024. szeptember</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2024. október</c:v>
@@ -6232,7 +6229,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -6561,414 +6558,414 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="18">
+      <c r="C1" s="22">
         <v>45108</v>
       </c>
-      <c r="D1" s="18">
+      <c r="D1" s="22">
         <v>45139</v>
       </c>
-      <c r="E1" s="18">
+      <c r="E1" s="22">
         <v>45170</v>
       </c>
-      <c r="F1" s="18">
+      <c r="F1" s="22">
         <v>45200</v>
       </c>
-      <c r="G1" s="18">
+      <c r="G1" s="22">
         <v>45231</v>
       </c>
-      <c r="H1" s="18">
+      <c r="H1" s="22">
         <v>45261</v>
       </c>
-      <c r="I1" s="18">
+      <c r="I1" s="22">
         <v>45292</v>
       </c>
-      <c r="J1" s="18">
+      <c r="J1" s="22">
         <v>45323</v>
       </c>
-      <c r="K1" s="18">
+      <c r="K1" s="22">
         <v>45352</v>
       </c>
-      <c r="L1" s="18">
+      <c r="L1" s="22">
         <v>45383</v>
       </c>
-      <c r="M1" s="18">
+      <c r="M1" s="22">
         <v>45413</v>
       </c>
-      <c r="N1" s="18">
+      <c r="N1" s="22">
         <v>45444</v>
       </c>
-      <c r="O1" s="18">
+      <c r="O1" s="22">
         <v>45474</v>
       </c>
-      <c r="P1" s="18">
+      <c r="P1" s="22">
         <v>45505</v>
       </c>
-      <c r="Q1" s="18">
+      <c r="Q1" s="22">
         <v>45536</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="T1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="U1" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="X1" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="Y1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="16" t="s">
+      <c r="Z1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="AA1" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="AB1" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AC1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AD1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AE1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AF1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="AE1" s="16" t="s">
+      <c r="AG1" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="16" t="s">
+      <c r="AH1" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="AG1" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH1" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="AI1" s="15"/>
-      <c r="AJ1" s="21">
+      <c r="AJ1" s="17">
         <v>2023</v>
       </c>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="21">
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="17">
         <v>2024</v>
       </c>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="22"/>
-      <c r="AR1" s="22"/>
-      <c r="AS1" s="22"/>
-      <c r="AT1" s="22"/>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
-      <c r="AW1" s="22"/>
-      <c r="AX1" s="22"/>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="23"/>
-      <c r="BA1" s="21">
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
+      <c r="AR1" s="18"/>
+      <c r="AS1" s="18"/>
+      <c r="AT1" s="18"/>
+      <c r="AU1" s="18"/>
+      <c r="AV1" s="18"/>
+      <c r="AW1" s="18"/>
+      <c r="AX1" s="18"/>
+      <c r="AY1" s="18"/>
+      <c r="AZ1" s="19"/>
+      <c r="BA1" s="17">
         <v>2025</v>
       </c>
-      <c r="BB1" s="22"/>
-      <c r="BC1" s="22"/>
-      <c r="BD1" s="22"/>
-      <c r="BE1" s="22"/>
-      <c r="BF1" s="22"/>
-      <c r="BG1" s="22"/>
-      <c r="BH1" s="22"/>
-      <c r="BI1" s="22"/>
-      <c r="BJ1" s="22"/>
-      <c r="BK1" s="22"/>
-      <c r="BL1" s="23"/>
-      <c r="BM1" s="21">
+      <c r="BB1" s="18"/>
+      <c r="BC1" s="18"/>
+      <c r="BD1" s="18"/>
+      <c r="BE1" s="18"/>
+      <c r="BF1" s="18"/>
+      <c r="BG1" s="18"/>
+      <c r="BH1" s="18"/>
+      <c r="BI1" s="18"/>
+      <c r="BJ1" s="18"/>
+      <c r="BK1" s="18"/>
+      <c r="BL1" s="19"/>
+      <c r="BM1" s="17">
         <v>2026</v>
       </c>
-      <c r="BN1" s="22"/>
-      <c r="BO1" s="22"/>
-      <c r="BP1" s="22"/>
-      <c r="BQ1" s="22"/>
-      <c r="BR1" s="22"/>
-      <c r="BS1" s="22"/>
-      <c r="BT1" s="22"/>
-      <c r="BU1" s="22"/>
-      <c r="BV1" s="22"/>
-      <c r="BW1" s="22"/>
-      <c r="BX1" s="23"/>
+      <c r="BN1" s="18"/>
+      <c r="BO1" s="18"/>
+      <c r="BP1" s="18"/>
+      <c r="BQ1" s="18"/>
+      <c r="BR1" s="18"/>
+      <c r="BS1" s="18"/>
+      <c r="BT1" s="18"/>
+      <c r="BU1" s="18"/>
+      <c r="BV1" s="18"/>
+      <c r="BW1" s="18"/>
+      <c r="BX1" s="19"/>
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
       <c r="AI2" s="15"/>
       <c r="AJ2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AL2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AL2" s="11" t="s">
+      <c r="AM2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="AM2" s="11" t="s">
+      <c r="AN2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AO2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="AO2" s="11" t="s">
+      <c r="AP2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="AP2" s="11" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="11" t="s">
+      <c r="AR2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AS2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="AS2" s="11" t="s">
+      <c r="AT2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AT2" s="11" t="s">
+      <c r="AU2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AU2" s="11" t="s">
+      <c r="AV2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AV2" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="AW2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AX2" s="11" t="s">
+      <c r="AY2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="AY2" s="11" t="s">
+      <c r="AZ2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="AZ2" s="11" t="s">
+      <c r="BA2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="BA2" s="11" t="s">
+      <c r="BB2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="BB2" s="11" t="s">
+      <c r="BC2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="BC2" s="11" t="s">
+      <c r="BD2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="BD2" s="11" t="s">
+      <c r="BE2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="BE2" s="11" t="s">
+      <c r="BF2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="BF2" s="11" t="s">
+      <c r="BG2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BH2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="BH2" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="BI2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="BJ2" s="11" t="s">
+      <c r="BK2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="BK2" s="11" t="s">
+      <c r="BL2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="BL2" s="11" t="s">
+      <c r="BM2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="BM2" s="11" t="s">
+      <c r="BN2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="BN2" s="11" t="s">
+      <c r="BO2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="BO2" s="11" t="s">
+      <c r="BP2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="BP2" s="11" t="s">
+      <c r="BQ2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="BQ2" s="11" t="s">
+      <c r="BR2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="BR2" s="11" t="s">
+      <c r="BS2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="BS2" s="11" t="s">
+      <c r="BT2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="BT2" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="BU2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="BV2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="BV2" s="11" t="s">
+      <c r="BW2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="BW2" s="11" t="s">
+      <c r="BX2" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="BX2" s="11" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="17">
+      <c r="A3" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="16">
         <v>1636</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>1695</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="16">
         <v>1616</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="16">
         <v>1770</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="16">
         <v>1882</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="16">
         <v>1517</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="16">
         <v>1877</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="16">
         <v>1672</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="16">
         <v>1475</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="16">
         <v>1795</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="16">
         <v>1874</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="16">
         <v>1859</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="16">
         <v>1895</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="16">
         <v>1676</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="16">
         <v>1826</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="16">
         <v>1750</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="16">
         <v>1608</v>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="16">
         <v>1377</v>
       </c>
-      <c r="U3" s="17">
+      <c r="U3" s="16">
         <v>1743</v>
       </c>
-      <c r="V3" s="17">
+      <c r="V3" s="16">
         <v>1415</v>
       </c>
-      <c r="W3" s="17">
+      <c r="W3" s="16">
         <v>1513</v>
       </c>
-      <c r="X3" s="17">
+      <c r="X3" s="16">
         <v>2001</v>
       </c>
-      <c r="Y3" s="17">
+      <c r="Y3" s="16">
         <v>1923</v>
       </c>
-      <c r="Z3" s="17">
+      <c r="Z3" s="16">
         <v>1997</v>
       </c>
-      <c r="AA3" s="17">
+      <c r="AA3" s="16">
         <v>2288</v>
       </c>
-      <c r="AB3" s="17">
+      <c r="AB3" s="16">
         <v>1742</v>
       </c>
-      <c r="AC3" s="17">
+      <c r="AC3" s="16">
         <v>2095</v>
       </c>
-      <c r="AD3" s="17">
+      <c r="AD3" s="16">
         <v>2089</v>
       </c>
-      <c r="AE3" s="17">
+      <c r="AE3" s="16">
         <v>1959</v>
       </c>
-      <c r="AF3" s="17">
+      <c r="AF3" s="16">
         <v>1722</v>
       </c>
-      <c r="AG3" s="17">
+      <c r="AG3" s="16">
         <v>2254</v>
       </c>
-      <c r="AH3" s="17">
+      <c r="AH3" s="16">
         <v>1995</v>
       </c>
       <c r="AI3" s="14"/>
@@ -7102,141 +7099,141 @@
       </c>
     </row>
     <row r="4" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="17"/>
-      <c r="AC4" s="17"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="17"/>
-      <c r="AF4" s="17"/>
-      <c r="AG4" s="17"/>
-      <c r="AH4" s="17"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
       <c r="AI4" s="14"/>
     </row>
     <row r="5" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="17">
+      <c r="A5" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="16">
         <v>4233</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <v>4596</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>4183</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="16">
         <v>4083</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="16">
         <v>4421</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <v>3833</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <v>4269</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="16">
         <v>3816</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="16">
         <v>3440</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="16">
         <v>3995</v>
       </c>
-      <c r="M5" s="17">
+      <c r="M5" s="16">
         <v>4212</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="16">
         <v>4312</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="16">
         <v>4491</v>
       </c>
-      <c r="P5" s="17">
+      <c r="P5" s="16">
         <v>4099</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="16">
         <v>4595</v>
       </c>
-      <c r="R5" s="17">
+      <c r="R5" s="16">
         <v>4571</v>
       </c>
-      <c r="S5" s="17">
+      <c r="S5" s="16">
         <v>3964</v>
       </c>
-      <c r="T5" s="17">
+      <c r="T5" s="16">
         <v>3625</v>
       </c>
-      <c r="U5" s="17">
+      <c r="U5" s="16">
         <v>6616</v>
       </c>
-      <c r="V5" s="17">
+      <c r="V5" s="16">
         <v>5144</v>
       </c>
-      <c r="W5" s="17">
+      <c r="W5" s="16">
         <v>5443</v>
       </c>
-      <c r="X5" s="17">
+      <c r="X5" s="16">
         <v>5976</v>
       </c>
-      <c r="Y5" s="17">
+      <c r="Y5" s="16">
         <v>6586</v>
       </c>
-      <c r="Z5" s="17">
+      <c r="Z5" s="16">
         <v>6177</v>
       </c>
-      <c r="AA5" s="17">
+      <c r="AA5" s="16">
         <v>6987</v>
       </c>
-      <c r="AB5" s="17">
+      <c r="AB5" s="16">
         <v>5825</v>
       </c>
-      <c r="AC5" s="17">
+      <c r="AC5" s="16">
         <v>5045</v>
       </c>
-      <c r="AD5" s="17">
+      <c r="AD5" s="16">
         <v>4754</v>
       </c>
-      <c r="AE5" s="17">
+      <c r="AE5" s="16">
         <v>4969</v>
       </c>
-      <c r="AF5" s="17">
+      <c r="AF5" s="16">
         <v>4203</v>
       </c>
-      <c r="AG5" s="17">
+      <c r="AG5" s="16">
         <v>4425</v>
       </c>
-      <c r="AH5" s="17">
+      <c r="AH5" s="16">
         <v>4096</v>
       </c>
       <c r="AI5" s="14"/>
@@ -7370,141 +7367,141 @@
       </c>
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="17"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="16"/>
       <c r="AI6" s="14"/>
     </row>
     <row r="7" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="17">
+      <c r="A7" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="16">
         <v>1162</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>1272</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>1298</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <v>1160</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>1319</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>1196</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="20">
         <v>1339</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>1177</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>1111</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <v>1172</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="16">
         <v>1173</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="16">
         <v>1283</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>1234</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="16">
         <v>1063</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="16">
         <v>1409</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="16">
         <v>1306</v>
       </c>
-      <c r="S7" s="17">
+      <c r="S7" s="16">
         <v>1227</v>
       </c>
-      <c r="T7" s="17">
+      <c r="T7" s="16">
         <v>1054</v>
       </c>
-      <c r="U7" s="17">
+      <c r="U7" s="16">
         <v>1285</v>
       </c>
-      <c r="V7" s="17">
+      <c r="V7" s="16">
         <v>978</v>
       </c>
-      <c r="W7" s="17">
+      <c r="W7" s="16">
         <v>1025</v>
       </c>
-      <c r="X7" s="17">
+      <c r="X7" s="16">
         <v>922</v>
       </c>
-      <c r="Y7" s="17">
+      <c r="Y7" s="16">
         <v>1150</v>
       </c>
-      <c r="Z7" s="17">
+      <c r="Z7" s="16">
         <v>1082</v>
       </c>
-      <c r="AA7" s="17">
+      <c r="AA7" s="16">
         <v>1304</v>
       </c>
-      <c r="AB7" s="17">
+      <c r="AB7" s="16">
         <v>1075</v>
       </c>
-      <c r="AC7" s="17">
+      <c r="AC7" s="16">
         <v>1202</v>
       </c>
-      <c r="AD7" s="17">
+      <c r="AD7" s="16">
         <v>1164</v>
       </c>
-      <c r="AE7" s="17">
+      <c r="AE7" s="16">
         <v>1201</v>
       </c>
-      <c r="AF7" s="17">
+      <c r="AF7" s="16">
         <v>1109</v>
       </c>
-      <c r="AG7" s="17">
+      <c r="AG7" s="16">
         <v>1333</v>
       </c>
-      <c r="AH7" s="17">
+      <c r="AH7" s="16">
         <v>1099</v>
       </c>
       <c r="AI7" s="14"/>
@@ -7638,141 +7635,141 @@
       </c>
     </row>
     <row r="8" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
       <c r="AI8" s="14"/>
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="17">
+      <c r="A9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="16">
         <v>395</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>415</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>352</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="16">
         <v>317</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="16">
         <v>302</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="16">
         <v>270</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="16">
         <v>360</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="16">
         <v>358</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>306</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="16">
         <v>356</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="16">
         <v>396</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="16">
         <v>371</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <v>415</v>
       </c>
-      <c r="P9" s="17">
+      <c r="P9" s="16">
         <v>364</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="16">
         <v>323</v>
       </c>
-      <c r="R9" s="17">
+      <c r="R9" s="16">
         <v>324</v>
       </c>
-      <c r="S9" s="17">
+      <c r="S9" s="16">
         <v>285</v>
       </c>
-      <c r="T9" s="17">
+      <c r="T9" s="16">
         <v>223</v>
       </c>
-      <c r="U9" s="17">
+      <c r="U9" s="16">
         <v>326</v>
       </c>
-      <c r="V9" s="17">
+      <c r="V9" s="16">
         <v>286</v>
       </c>
-      <c r="W9" s="17">
+      <c r="W9" s="16">
         <v>414</v>
       </c>
-      <c r="X9" s="17">
+      <c r="X9" s="16">
         <v>358</v>
       </c>
-      <c r="Y9" s="17">
+      <c r="Y9" s="16">
         <v>471</v>
       </c>
-      <c r="Z9" s="17">
+      <c r="Z9" s="16">
         <v>409</v>
       </c>
-      <c r="AA9" s="17">
+      <c r="AA9" s="16">
         <v>469</v>
       </c>
-      <c r="AB9" s="17">
+      <c r="AB9" s="16">
         <v>404</v>
       </c>
-      <c r="AC9" s="17">
+      <c r="AC9" s="16">
         <v>417</v>
       </c>
-      <c r="AD9" s="17">
+      <c r="AD9" s="16">
         <v>315</v>
       </c>
-      <c r="AE9" s="17">
+      <c r="AE9" s="16">
         <v>321</v>
       </c>
-      <c r="AF9" s="17">
+      <c r="AF9" s="16">
         <v>293</v>
       </c>
-      <c r="AG9" s="17">
+      <c r="AG9" s="16">
         <v>308</v>
       </c>
-      <c r="AH9" s="17">
+      <c r="AH9" s="16">
         <v>329</v>
       </c>
       <c r="AI9" s="14"/>
@@ -7906,141 +7903,141 @@
       </c>
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="16"/>
       <c r="AI10" s="14"/>
     </row>
     <row r="11" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="17">
+      <c r="A11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="16">
         <v>233</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>294</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>242</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <v>183</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>206</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <v>161</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="16">
         <v>198</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <v>203</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>189</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="16">
         <v>218</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="16">
         <v>226</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="16">
         <v>190</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="16">
         <v>205</v>
       </c>
-      <c r="P11" s="17">
+      <c r="P11" s="16">
         <v>186</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="Q11" s="16">
         <v>219</v>
       </c>
-      <c r="R11" s="17">
+      <c r="R11" s="16">
         <v>219</v>
       </c>
-      <c r="S11" s="17">
+      <c r="S11" s="16">
         <v>192</v>
       </c>
-      <c r="T11" s="17">
+      <c r="T11" s="16">
         <v>140</v>
       </c>
-      <c r="U11" s="17">
+      <c r="U11" s="16">
         <v>219</v>
       </c>
-      <c r="V11" s="17">
+      <c r="V11" s="16">
         <v>198</v>
       </c>
-      <c r="W11" s="17">
+      <c r="W11" s="16">
         <v>151</v>
       </c>
-      <c r="X11" s="17">
+      <c r="X11" s="16">
         <v>173</v>
       </c>
-      <c r="Y11" s="17">
+      <c r="Y11" s="16">
         <v>207</v>
       </c>
-      <c r="Z11" s="17">
+      <c r="Z11" s="16">
         <v>219</v>
       </c>
-      <c r="AA11" s="17">
+      <c r="AA11" s="16">
         <v>197</v>
       </c>
-      <c r="AB11" s="17">
+      <c r="AB11" s="16">
         <v>218</v>
       </c>
-      <c r="AC11" s="17">
+      <c r="AC11" s="16">
         <v>264</v>
       </c>
-      <c r="AD11" s="17">
+      <c r="AD11" s="16">
         <v>265</v>
       </c>
-      <c r="AE11" s="17">
+      <c r="AE11" s="16">
         <v>240</v>
       </c>
-      <c r="AF11" s="17">
+      <c r="AF11" s="16">
         <v>204</v>
       </c>
-      <c r="AG11" s="17">
+      <c r="AG11" s="16">
         <v>222</v>
       </c>
-      <c r="AH11" s="17">
+      <c r="AH11" s="16">
         <v>268</v>
       </c>
       <c r="AI11" s="14"/>
@@ -8174,141 +8171,141 @@
       </c>
     </row>
     <row r="12" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
       <c r="AI12" s="14"/>
     </row>
     <row r="13" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="17">
+      <c r="A13" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="16">
         <v>96</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <v>87</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>74</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="16">
         <v>99</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="16">
         <v>83</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <v>68</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20">
         <v>110</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="16">
         <v>103</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="16">
         <v>76</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="16">
         <v>94</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="16">
         <v>88</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="16">
         <v>100</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="16">
         <v>102</v>
       </c>
-      <c r="P13" s="17">
+      <c r="P13" s="16">
         <v>73</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="16">
         <v>93</v>
       </c>
-      <c r="R13" s="17">
+      <c r="R13" s="16">
         <v>106</v>
       </c>
-      <c r="S13" s="17">
+      <c r="S13" s="16">
         <v>107</v>
       </c>
-      <c r="T13" s="17">
+      <c r="T13" s="16">
         <v>81</v>
       </c>
-      <c r="U13" s="17">
+      <c r="U13" s="16">
         <v>107</v>
       </c>
-      <c r="V13" s="17">
+      <c r="V13" s="16">
         <v>89</v>
       </c>
-      <c r="W13" s="17">
+      <c r="W13" s="16">
         <v>91</v>
       </c>
-      <c r="X13" s="17">
+      <c r="X13" s="16">
         <v>116</v>
       </c>
-      <c r="Y13" s="17">
+      <c r="Y13" s="16">
         <v>107</v>
       </c>
-      <c r="Z13" s="17">
+      <c r="Z13" s="16">
         <v>96</v>
       </c>
-      <c r="AA13" s="17">
+      <c r="AA13" s="16">
         <v>146</v>
       </c>
-      <c r="AB13" s="17">
+      <c r="AB13" s="16">
         <v>105</v>
       </c>
-      <c r="AC13" s="17">
+      <c r="AC13" s="16">
         <v>107</v>
       </c>
-      <c r="AD13" s="17">
+      <c r="AD13" s="16">
         <v>128</v>
       </c>
-      <c r="AE13" s="17">
+      <c r="AE13" s="16">
         <v>127</v>
       </c>
-      <c r="AF13" s="17">
+      <c r="AF13" s="16">
         <v>68</v>
       </c>
-      <c r="AG13" s="17">
+      <c r="AG13" s="16">
         <v>117</v>
       </c>
-      <c r="AH13" s="17">
+      <c r="AH13" s="16">
         <v>99</v>
       </c>
       <c r="AI13" s="14"/>
@@ -8442,40 +8439,40 @@
       </c>
     </row>
     <row r="14" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="17"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="16"/>
       <c r="AI14" s="14"/>
       <c r="AJ14" s="7"/>
       <c r="AK14" s="7"/>
@@ -8532,78 +8529,189 @@
     <row r="16" spans="1:76" x14ac:dyDescent="0.25">
       <c r="B16" s="5"/>
       <c r="C16" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="234">
-    <mergeCell ref="AG9:AG10"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AO1:AZ1"/>
-    <mergeCell ref="BA1:BL1"/>
-    <mergeCell ref="BM1:BX1"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AH13:AH14"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF1:AF2"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AG1:AG2"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AC1:AC2"/>
+    <mergeCell ref="AD1:AD2"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AC9:AC10"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="AJ1:AN1"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="AH1:AH2"/>
+    <mergeCell ref="AH3:AH4"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="H7:H8"/>
     <mergeCell ref="A11:B12"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -8628,187 +8736,76 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="AG9:AG10"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="AO1:AZ1"/>
+    <mergeCell ref="BA1:BL1"/>
+    <mergeCell ref="BM1:BX1"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
     <mergeCell ref="K1:K2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="K5:K6"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="H7:H8"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="X9:X10"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="AJ1:AN1"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="Y9:Y10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="AE1:AE2"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AC1:AC2"/>
-    <mergeCell ref="AD1:AD2"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AC9:AC10"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AD5:AD6"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AD9:AD10"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AB9:AB10"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AH1:AH2"/>
-    <mergeCell ref="AH3:AH4"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AH9:AH10"/>
-    <mergeCell ref="AH11:AH12"/>
-    <mergeCell ref="AH13:AH14"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AE5:AE6"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AE9:AE10"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF1:AF2"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AF9:AF10"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AG1:AG2"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AG7:AG8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AJ3:BO3 AJ5:BO5 AJ7:BO7 AJ9:BO9 AJ11:BO11 AJ13:BO13">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C3:AH4">
     <cfRule type="expression" priority="2">
       <formula>MAX($C$3:$AH$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH3:AH4">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MAX($C$3:$AH$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ3:BO3 AJ5:BO5 AJ7:BO7 AJ9:BO9 AJ11:BO11 AJ13:BO13">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
